--- a/output/北海道_上下水道経営戦略_改訂時期一覧.xlsx
+++ b/output/北海道_上下水道経営戦略_改訂時期一覧.xlsx
@@ -226,7 +226,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T3025" displayName="T3025" ref="A2:O297" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2344" displayName="T2344" ref="A2:O297" headerRowCount="1">
   <autoFilter ref="A2:O297"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -250,7 +250,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T11620" displayName="T11620" ref="A2:O51" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T56999" displayName="T56999" ref="A2:O51" headerRowCount="1">
   <autoFilter ref="A2:O51"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T21148" displayName="T21148" ref="A2:O13" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T68584" displayName="T68584" ref="A2:O13" headerRowCount="1">
   <autoFilter ref="A2:O13"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T98985" displayName="T98985" ref="A2:O114" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T31505" displayName="T31505" ref="A2:O114" headerRowCount="1">
   <autoFilter ref="A2:O114"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T70114" displayName="T70114" ref="A2:O18" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T7389" displayName="T7389" ref="A2:O18" headerRowCount="1">
   <autoFilter ref="A2:O18"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T30486" displayName="T30486" ref="A2:O105" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T11350" displayName="T11350" ref="A2:O105" headerRowCount="1">
   <autoFilter ref="A2:O105"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T40732" displayName="T40732" ref="A2:O95" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T7057" displayName="T7057" ref="A2:O95" headerRowCount="1">
   <autoFilter ref="A2:O95"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
